--- a/public/templates/Code_on_Wages/Form I - Register of Fines.xlsx
+++ b/public/templates/Code_on_Wages/Form I - Register of Fines.xlsx
@@ -304,7 +304,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -327,6 +327,13 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -353,76 +360,88 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -681,396 +700,396 @@
   <dimension ref="A1:P25"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="9" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="H4" s="5" t="s">
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="H4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="H5" s="5" t="s">
+      <c r="B5" s="4"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="H5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="6"/>
+      <c r="J5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="6" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="6" t="s">
+      <c r="B7" s="4"/>
+      <c r="C7" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="K9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="M9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="O9" s="7" t="s">
+      <c r="O9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="P9" s="7" t="s">
+      <c r="P9" s="8" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J11" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="K11" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="L11" s="10" t="s">
+      <c r="L11" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="M11" s="8" t="s">
+      <c r="M11" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="N11" s="10" t="s">
+      <c r="N11" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="O11" s="8" t="s">
+      <c r="O11" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="P11" s="8" t="s">
+      <c r="P11" s="11" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="12"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="15"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="9"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="12"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="15"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="9"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="13"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="12"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="15"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="15"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="18"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="K22" s="5" t="s">
+      <c r="K22" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="17" t="s">
+      <c r="F23" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K23" s="17" t="s">
+      <c r="K23" s="20" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="K24" s="17" t="s">
+      <c r="K24" s="20" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="F25" s="17" t="s">
+      <c r="F25" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="K25" s="17" t="s">
+      <c r="K25" s="20" t="s">
         <v>50</v>
       </c>
     </row>
